--- a/objects/cancer_type.xlsx
+++ b/objects/cancer_type.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t xml:space="preserve">model</t>
   </si>
@@ -25,6 +25,9 @@
     <t xml:space="preserve">term</t>
   </si>
   <si>
+    <t xml:space="preserve">Severe COVID</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hospitalized</t>
   </si>
   <si>
@@ -40,295 +43,376 @@
     <t xml:space="preserve">Breast cancer</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68 (1.37, 2.07)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26 (0.84, 1.89)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99 (2.01, 4.46)</t>
+    <t xml:space="preserve">1.77 (1.47, 2.14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70 (1.40, 2.06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22 (0.82, 1.81)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86 (1.95, 4.19)</t>
   </si>
   <si>
     <t xml:space="preserve">unadjusted_firth</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69 (1.36, 2.07)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29 (0.84, 1.88)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04 (2.00, 4.43)</t>
+    <t xml:space="preserve">1.78 (1.47, 2.14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70 (1.39, 2.06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24 (0.82, 1.80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90 (1.94, 4.17)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment1</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18 (0.94, 1.46)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02 (0.66, 1.52)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52 (0.98, 2.26)</t>
+    <t xml:space="preserve">1.15 (0.94, 1.39)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17 (0.95, 1.42)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98 (0.64, 1.44)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37 (0.90, 2.01)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment2</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26 (1.00, 1.59)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11 (0.71, 1.67)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71 (1.09, 2.59)</t>
+    <t xml:space="preserve">1.23 (0.99, 1.51)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26 (1.01, 1.56)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11 (0.71, 1.64)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43 (0.92, 2.14)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment3</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33 (1.03, 1.68)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47 (0.91, 2.26)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76 (1.10, 2.73)</t>
+    <t xml:space="preserve">1.24 (0.99, 1.53)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28 (1.02, 1.60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45 (0.91, 2.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47 (0.93, 2.24)</t>
   </si>
   <si>
     <t xml:space="preserve">Hematologic malignancy</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91 (2.54, 3.34)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27 (1.78, 2.90)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93 (2.96, 5.21)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92 (2.54, 3.34)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29 (1.78, 2.90)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95 (2.96, 5.20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98 (1.72, 2.28)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50 (1.16, 1.92)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98 (1.47, 2.63)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13 (1.83, 2.47)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57 (1.20, 2.03)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96 (1.42, 2.65)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97 (1.67, 2.30)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88 (1.40, 2.50)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73 (1.22, 2.42)</t>
+    <t xml:space="preserve">3.11 (2.75, 3.51)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93 (2.58, 3.33)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38 (1.89, 3.00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94 (3.02, 5.14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11 (2.75, 3.50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39 (1.89, 2.99)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96 (3.02, 5.13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06 (1.81, 2.33)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00 (1.75, 2.27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58 (1.24, 1.98)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97 (1.49, 2.57)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19 (1.91, 2.50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14 (1.86, 2.46)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62 (1.25, 2.07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83 (1.35, 2.44)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95 (1.69, 2.25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94 (1.67, 2.25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91 (1.44, 2.50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57 (1.12, 2.15)</t>
   </si>
   <si>
     <t xml:space="preserve">Lung cancer</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46 (3.51, 5.67)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68 (1.70, 4.23)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48 (4.16, 10.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48 (3.51, 5.66)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74 (1.69, 4.19)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61 (4.14, 10.03)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29 (1.78, 2.92)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34 (0.82, 2.07)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03 (1.26, 3.13)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43 (1.85, 3.15)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19 (0.69, 1.93)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39 (0.77, 2.33)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60 (1.97, 3.41)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57 (0.88, 2.60)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36 (0.73, 2.34)</t>
+    <t xml:space="preserve">4.88 (3.93, 6.06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36 (3.47, 5.48)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57 (1.63, 4.05)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81 (4.49, 10.34)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90 (3.93, 6.06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38 (3.47, 5.47)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63 (1.63, 4.02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93 (4.48, 10.27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32 (1.85, 2.89)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19 (1.72, 2.76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26 (0.78, 1.95)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07 (1.32, 3.10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32 (1.81, 2.95)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34 (1.81, 3.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24 (0.73, 1.98)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52 (0.89, 2.45)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34 (1.81, 3.00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41 (1.85, 3.12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61 (0.92, 2.61)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44 (0.82, 2.36)</t>
   </si>
   <si>
     <t xml:space="preserve">Melanoma</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87 (1.55, 2.26)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17 (0.79, 1.72)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23 (2.26, 4.63)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88 (1.55, 2.25)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19 (0.79, 1.71)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28 (2.25, 4.61)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08 (0.89, 1.30)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69 (0.46, 1.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15 (0.78, 1.64)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15 (0.93, 1.41)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74 (0.47, 1.10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21 (0.80, 1.76)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20 (0.97, 1.49)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96 (0.61, 1.46)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20 (0.78, 1.78)</t>
+    <t xml:space="preserve">1.90 (1.60, 2.25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82 (1.52, 2.17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16 (0.80, 1.69)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11 (2.21, 4.39)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18 (0.79, 1.68)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15 (2.20, 4.37)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02 (0.85, 1.21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04 (0.86, 1.24)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.68 (0.46, 0.98)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06 (0.74, 1.49)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11 (0.92, 1.33)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13 (0.93, 1.37)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.74 (0.49, 1.09)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12 (0.76, 1.60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11 (0.91, 1.34)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16 (0.95, 1.42)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96 (0.62, 1.43)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08 (0.72, 1.56)</t>
   </si>
   <si>
     <t xml:space="preserve">Other cancer</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48 (1.33, 1.66)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27 (1.04, 1.55)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48 (1.98, 3.10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49 (1.33, 1.66)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04 (0.93, 1.17)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91 (0.74, 1.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32 (1.05, 1.66)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09 (0.96, 1.23)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90 (0.72, 1.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27 (0.99, 1.63)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13 (0.99, 1.28)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17 (0.92, 1.49)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36 (1.03, 1.77)</t>
+    <t xml:space="preserve">1.67 (1.52, 1.84)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55 (1.40, 1.72)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29 (1.06, 1.56)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59 (2.10, 3.19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68 (1.52, 1.84)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60 (2.10, 3.19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13 (1.02, 1.24)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08 (0.97, 1.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92 (0.75, 1.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36 (1.09, 1.68)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16 (1.04, 1.29)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12 (1.00, 1.26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89 (0.72, 1.10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24 (0.97, 1.56)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15 (1.02, 1.28)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13 (1.00, 1.27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15 (0.91, 1.45)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26 (0.98, 1.62)</t>
   </si>
   <si>
     <t xml:space="preserve">Prostate cancer</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12 (1.73, 2.61)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52 (1.02, 2.26)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59 (2.42, 5.32)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13 (1.73, 2.60)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55 (1.02, 2.25)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65 (2.42, 5.29)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71 (0.57, 0.88)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45 (0.29, 0.66)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63 (0.41, 0.93)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72 (0.56, 0.90)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48 (0.31, 0.73)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69 (0.44, 1.03)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85 (0.65, 1.08)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71 (0.43, 1.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81 (0.51, 1.24)</t>
+    <t xml:space="preserve">2.35 (1.96, 2.82)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08 (1.71, 2.53)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57 (1.07, 2.31)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78 (2.62, 5.46)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36 (1.96, 2.82)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09 (1.71, 2.53)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60 (1.07, 2.29)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83 (2.61, 5.43)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.74 (0.61, 0.89)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71 (0.57, 0.86)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47 (0.31, 0.68)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.66 (0.44, 0.95)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77 (0.63, 0.95)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73 (0.58, 0.91)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49 (0.31, 0.73)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69 (0.45, 1.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89 (0.71, 1.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85 (0.66, 1.07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71 (0.43, 1.09)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79 (0.51, 1.18)</t>
   </si>
 </sst>
 </file>
@@ -673,90 +757,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -786,90 +888,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>35</v>
+      </c>
+      <c r="F2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>38</v>
+      </c>
+      <c r="F3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="F4" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>46</v>
+      </c>
+      <c r="F5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>50</v>
+      </c>
+      <c r="F6" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -899,90 +1019,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>55</v>
+      </c>
+      <c r="F2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>59</v>
+      </c>
+      <c r="F3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>63</v>
+      </c>
+      <c r="F4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>67</v>
+      </c>
+      <c r="F5" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>57</v>
+        <v>71</v>
+      </c>
+      <c r="F6" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1012,90 +1150,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>76</v>
+      </c>
+      <c r="F2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>64</v>
+        <v>78</v>
+      </c>
+      <c r="F3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>67</v>
+        <v>82</v>
+      </c>
+      <c r="F4" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>86</v>
+      </c>
+      <c r="F5" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>90</v>
+      </c>
+      <c r="F6" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1125,90 +1281,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>95</v>
+      </c>
+      <c r="F2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>95</v>
+      </c>
+      <c r="F3" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>81</v>
+        <v>101</v>
+      </c>
+      <c r="F4" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>84</v>
+        <v>105</v>
+      </c>
+      <c r="F5" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
-        <v>87</v>
+        <v>109</v>
+      </c>
+      <c r="F6" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1238,90 +1412,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>114</v>
+      </c>
+      <c r="F2" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
-        <v>94</v>
+        <v>118</v>
+      </c>
+      <c r="F3" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="E4" t="s">
-        <v>97</v>
+        <v>122</v>
+      </c>
+      <c r="F4" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>126</v>
+      </c>
+      <c r="F5" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>130</v>
+      </c>
+      <c r="F6" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/objects/cancer_type.xlsx
+++ b/objects/cancer_type.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
   <si>
     <t xml:space="preserve">model</t>
   </si>
@@ -88,7 +88,7 @@
     <t xml:space="preserve">adjustment2</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23 (0.99, 1.51)</t>
+    <t xml:space="preserve">1.23 (1.00, 1.51)</t>
   </si>
   <si>
     <t xml:space="preserve">1.26 (1.01, 1.56)</t>
@@ -103,13 +103,13 @@
     <t xml:space="preserve">adjustment3</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24 (0.99, 1.53)</t>
+    <t xml:space="preserve">1.23 (0.99, 1.53)</t>
   </si>
   <si>
     <t xml:space="preserve">1.28 (1.02, 1.60)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45 (0.91, 2.20)</t>
+    <t xml:space="preserve">1.44 (0.90, 2.20)</t>
   </si>
   <si>
     <t xml:space="preserve">1.47 (0.93, 2.24)</t>
@@ -139,28 +139,28 @@
     <t xml:space="preserve">3.96 (3.02, 5.13)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06 (1.81, 2.33)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00 (1.75, 2.27)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58 (1.24, 1.98)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97 (1.49, 2.57)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19 (1.91, 2.50)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14 (1.86, 2.46)</t>
+    <t xml:space="preserve">2.07 (1.82, 2.35)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01 (1.76, 2.29)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57 (1.23, 1.98)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96 (1.48, 2.56)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20 (1.92, 2.51)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15 (1.87, 2.47)</t>
   </si>
   <si>
     <t xml:space="preserve">1.62 (1.25, 2.07)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83 (1.35, 2.44)</t>
+    <t xml:space="preserve">1.83 (1.35, 2.43)</t>
   </si>
   <si>
     <t xml:space="preserve">1.95 (1.69, 2.25)</t>
@@ -202,34 +202,34 @@
     <t xml:space="preserve">6.93 (4.48, 10.27)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32 (1.85, 2.89)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19 (1.72, 2.76)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26 (0.78, 1.95)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07 (1.32, 3.10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32 (1.81, 2.95)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34 (1.81, 3.01)</t>
+    <t xml:space="preserve">2.33 (1.85, 2.91)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20 (1.73, 2.77)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26 (0.77, 1.94)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06 (1.32, 3.09)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32 (1.81, 2.96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35 (1.82, 3.01)</t>
   </si>
   <si>
     <t xml:space="preserve">1.24 (0.73, 1.98)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52 (0.89, 2.45)</t>
+    <t xml:space="preserve">1.52 (0.89, 2.44)</t>
   </si>
   <si>
     <t xml:space="preserve">2.34 (1.81, 3.00)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41 (1.85, 3.12)</t>
+    <t xml:space="preserve">2.41 (1.85, 3.11)</t>
   </si>
   <si>
     <t xml:space="preserve">1.61 (0.92, 2.61)</t>
@@ -259,10 +259,10 @@
     <t xml:space="preserve">3.15 (2.20, 4.37)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02 (0.85, 1.21)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04 (0.86, 1.24)</t>
+    <t xml:space="preserve">1.01 (0.85, 1.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03 (0.86, 1.24)</t>
   </si>
   <si>
     <t xml:space="preserve">0.68 (0.46, 0.98)</t>
@@ -271,10 +271,10 @@
     <t xml:space="preserve">1.06 (0.74, 1.49)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11 (0.92, 1.33)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13 (0.93, 1.37)</t>
+    <t xml:space="preserve">1.10 (0.91, 1.33)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13 (0.92, 1.36)</t>
   </si>
   <si>
     <t xml:space="preserve">0.74 (0.49, 1.09)</t>
@@ -283,13 +283,13 @@
     <t xml:space="preserve">1.12 (0.76, 1.60)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11 (0.91, 1.34)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16 (0.95, 1.42)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96 (0.62, 1.43)</t>
+    <t xml:space="preserve">1.10 (0.90, 1.33)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15 (0.94, 1.41)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95 (0.61, 1.42)</t>
   </si>
   <si>
     <t xml:space="preserve">1.08 (0.72, 1.56)</t>
@@ -316,40 +316,40 @@
     <t xml:space="preserve">2.60 (2.10, 3.19)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13 (1.02, 1.24)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08 (0.97, 1.20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92 (0.75, 1.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36 (1.09, 1.68)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16 (1.04, 1.29)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12 (1.00, 1.26)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89 (0.72, 1.10)</t>
+    <t xml:space="preserve">1.13 (1.02, 1.25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09 (0.98, 1.21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91 (0.75, 1.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35 (1.08, 1.67)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17 (1.04, 1.30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13 (1.01, 1.27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89 (0.71, 1.10)</t>
   </si>
   <si>
     <t xml:space="preserve">1.24 (0.97, 1.56)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15 (1.02, 1.28)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13 (1.00, 1.27)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15 (0.91, 1.45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26 (0.98, 1.62)</t>
+    <t xml:space="preserve">1.15 (1.02, 1.29)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13 (1.00, 1.28)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16 (0.91, 1.46)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27 (0.98, 1.62)</t>
   </si>
   <si>
     <t xml:space="preserve">Prostate cancer</t>
@@ -388,7 +388,7 @@
     <t xml:space="preserve">0.47 (0.31, 0.68)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66 (0.44, 0.95)</t>
+    <t xml:space="preserve">0.66 (0.45, 0.95)</t>
   </si>
   <si>
     <t xml:space="preserve">0.77 (0.63, 0.95)</t>
@@ -401,9 +401,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.69 (0.45, 1.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89 (0.71, 1.11)</t>
   </si>
   <si>
     <t xml:space="preserve">0.85 (0.66, 1.07)</t>
@@ -1504,16 +1501,16 @@
         <v>111</v>
       </c>
       <c r="C6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" t="s">
         <v>128</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>129</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>130</v>
-      </c>
-      <c r="F6" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
